--- a/salida/registro_cambios.xlsx
+++ b/salida/registro_cambios.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,46 +413,46 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H240"/>
+  <dimension ref="A1:H262"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Número BE</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Cliente</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Fecha</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Estado</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Detrack #</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Tracking Link</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Observaciones</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Registrado en</t>
         </is>
@@ -9911,6 +9899,814 @@
       <c r="H240" t="inlineStr">
         <is>
           <t>2026-03-13 16:32:44</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="n">
+        <v>8740</v>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>CR 26 No 23A - 41 BRR SAMPER MENDOZA, Bogotá, 00000</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>in_transit</t>
+        </is>
+      </c>
+      <c r="E241" t="inlineStr">
+        <is>
+          <t>DET6398291524</t>
+        </is>
+      </c>
+      <c r="F241" t="inlineStr">
+        <is>
+          <t>https://trk.la/aXLCBU6</t>
+        </is>
+      </c>
+      <c r="G241" t="inlineStr">
+        <is>
+          <t>✅ Orden creada</t>
+        </is>
+      </c>
+      <c r="H241" t="inlineStr">
+        <is>
+          <t>2026-05-15 11:36:02</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="n">
+        <v>8739</v>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>CL 17A No. 69 - 73, Bogotá, 00000</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>in_transit</t>
+        </is>
+      </c>
+      <c r="E242" t="inlineStr">
+        <is>
+          <t>DET6398291527</t>
+        </is>
+      </c>
+      <c r="F242" t="inlineStr">
+        <is>
+          <t>https://trk.la/aXLCB1T</t>
+        </is>
+      </c>
+      <c r="G242" t="inlineStr">
+        <is>
+          <t>✅ Orden creada</t>
+        </is>
+      </c>
+      <c r="H242" t="inlineStr">
+        <is>
+          <t>2026-05-15 11:36:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="n">
+        <v>8738</v>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>CL 5C No 35 - 05 BRR VERAGUAS, Bogotá, 111611</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>in_transit</t>
+        </is>
+      </c>
+      <c r="E243" t="inlineStr">
+        <is>
+          <t>DET6398291529</t>
+        </is>
+      </c>
+      <c r="F243" t="inlineStr">
+        <is>
+          <t>https://trk.la/aXLCBFw</t>
+        </is>
+      </c>
+      <c r="G243" t="inlineStr">
+        <is>
+          <t>✅ Orden creada</t>
+        </is>
+      </c>
+      <c r="H243" t="inlineStr">
+        <is>
+          <t>2026-05-15 11:36:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="n">
+        <v>8737</v>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>CR 3 56 - 07 EN 2 ZN IND CAZUCA, Soacha</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>in_transit</t>
+        </is>
+      </c>
+      <c r="E244" t="inlineStr">
+        <is>
+          <t>DET6398291531</t>
+        </is>
+      </c>
+      <c r="F244" t="inlineStr">
+        <is>
+          <t>https://trk.la/aXLCBrq</t>
+        </is>
+      </c>
+      <c r="G244" t="inlineStr">
+        <is>
+          <t>✅ Orden creada</t>
+        </is>
+      </c>
+      <c r="H244" t="inlineStr">
+        <is>
+          <t>2026-05-15 11:36:05</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr"/>
+      <c r="B245" t="inlineStr"/>
+      <c r="C245" t="inlineStr"/>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>Error</t>
+        </is>
+      </c>
+      <c r="E245" t="inlineStr"/>
+      <c r="F245" t="inlineStr"/>
+      <c r="G245" t="inlineStr">
+        <is>
+          <t>❌ Error en envío</t>
+        </is>
+      </c>
+      <c r="H245" t="inlineStr">
+        <is>
+          <t>2026-05-15 11:55:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr"/>
+      <c r="B246" t="inlineStr"/>
+      <c r="C246" t="inlineStr"/>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>Error</t>
+        </is>
+      </c>
+      <c r="E246" t="inlineStr"/>
+      <c r="F246" t="inlineStr"/>
+      <c r="G246" t="inlineStr">
+        <is>
+          <t>❌ Error en envío</t>
+        </is>
+      </c>
+      <c r="H246" t="inlineStr">
+        <is>
+          <t>2026-05-15 12:00:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr"/>
+      <c r="B247" t="inlineStr"/>
+      <c r="C247" t="inlineStr"/>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>Error</t>
+        </is>
+      </c>
+      <c r="E247" t="inlineStr"/>
+      <c r="F247" t="inlineStr"/>
+      <c r="G247" t="inlineStr">
+        <is>
+          <t>❌ Error en envío</t>
+        </is>
+      </c>
+      <c r="H247" t="inlineStr">
+        <is>
+          <t>2026-05-15 12:01:27</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>FAC-2026-001</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>Calle 123 #45-67, Ibagué</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>in_transit</t>
+        </is>
+      </c>
+      <c r="E248" t="inlineStr">
+        <is>
+          <t>DET6398293505</t>
+        </is>
+      </c>
+      <c r="F248" t="inlineStr">
+        <is>
+          <t>https://trk.la/aXLWZVM</t>
+        </is>
+      </c>
+      <c r="G248" t="inlineStr">
+        <is>
+          <t>✅ Orden creada</t>
+        </is>
+      </c>
+      <c r="H248" t="inlineStr">
+        <is>
+          <t>2026-05-15 12:03:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="n">
+        <v>754</v>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>CR 91 66 A 05, Bogotá, 11001</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>in_transit</t>
+        </is>
+      </c>
+      <c r="E249" t="inlineStr">
+        <is>
+          <t>DET6403024891</t>
+        </is>
+      </c>
+      <c r="F249" t="inlineStr">
+        <is>
+          <t>https://trk.la/aXg12iD</t>
+        </is>
+      </c>
+      <c r="G249" t="inlineStr">
+        <is>
+          <t>✅ Orden creada</t>
+        </is>
+      </c>
+      <c r="H249" t="inlineStr">
+        <is>
+          <t>2026-06-17 16:11:57</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="n">
+        <v>1642</v>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>CR 69 G 31 23 SUR, Bogotá, 110841</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>in_transit</t>
+        </is>
+      </c>
+      <c r="E250" t="inlineStr">
+        <is>
+          <t>DET6403024892</t>
+        </is>
+      </c>
+      <c r="F250" t="inlineStr">
+        <is>
+          <t>https://trk.la/aXg12hl</t>
+        </is>
+      </c>
+      <c r="G250" t="inlineStr">
+        <is>
+          <t>✅ Orden creada</t>
+        </is>
+      </c>
+      <c r="H250" t="inlineStr">
+        <is>
+          <t>2026-06-17 16:11:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="n">
+        <v>1641</v>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>CL 35 SUR No. 70 B 12, Bogotá, 110841</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>in_transit</t>
+        </is>
+      </c>
+      <c r="E251" t="inlineStr">
+        <is>
+          <t>DET6403024893</t>
+        </is>
+      </c>
+      <c r="F251" t="inlineStr">
+        <is>
+          <t>https://trk.la/aXg12ya</t>
+        </is>
+      </c>
+      <c r="G251" t="inlineStr">
+        <is>
+          <t>✅ Orden creada</t>
+        </is>
+      </c>
+      <c r="H251" t="inlineStr">
+        <is>
+          <t>2026-06-17 16:11:59</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="n">
+        <v>8818</v>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>CR 22 16 19, Bogotá, 111411</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>in_transit</t>
+        </is>
+      </c>
+      <c r="E252" t="inlineStr">
+        <is>
+          <t>DET6403024896</t>
+        </is>
+      </c>
+      <c r="F252" t="inlineStr">
+        <is>
+          <t>https://trk.la/aXg12az</t>
+        </is>
+      </c>
+      <c r="G252" t="inlineStr">
+        <is>
+          <t>✅ Orden creada</t>
+        </is>
+      </c>
+      <c r="H252" t="inlineStr">
+        <is>
+          <t>2026-06-17 16:12:01</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="n">
+        <v>8817</v>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>CL 70  54 - 17, Bogotá, 00000</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>in_transit</t>
+        </is>
+      </c>
+      <c r="E253" t="inlineStr">
+        <is>
+          <t>DET6403024921</t>
+        </is>
+      </c>
+      <c r="F253" t="inlineStr">
+        <is>
+          <t>https://trk.la/aXg12rn</t>
+        </is>
+      </c>
+      <c r="G253" t="inlineStr">
+        <is>
+          <t>✅ Orden creada</t>
+        </is>
+      </c>
+      <c r="H253" t="inlineStr">
+        <is>
+          <t>2026-06-17 16:12:02</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="n">
+        <v>8816</v>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>CR 53 No. 70 - 23, Bogotá, 111071</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>in_transit</t>
+        </is>
+      </c>
+      <c r="E254" t="inlineStr">
+        <is>
+          <t>DET6403024944</t>
+        </is>
+      </c>
+      <c r="F254" t="inlineStr">
+        <is>
+          <t>https://trk.la/aXg12GT</t>
+        </is>
+      </c>
+      <c r="G254" t="inlineStr">
+        <is>
+          <t>✅ Orden creada</t>
+        </is>
+      </c>
+      <c r="H254" t="inlineStr">
+        <is>
+          <t>2026-06-17 16:12:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="n">
+        <v>8815</v>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>CR 16 No 60 - 14 BRR LA ESMERALDA, Girón, 00000</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>in_transit</t>
+        </is>
+      </c>
+      <c r="E255" t="inlineStr">
+        <is>
+          <t>DET6403024962</t>
+        </is>
+      </c>
+      <c r="F255" t="inlineStr">
+        <is>
+          <t>https://trk.la/aXg1H60</t>
+        </is>
+      </c>
+      <c r="G255" t="inlineStr">
+        <is>
+          <t>✅ Orden creada</t>
+        </is>
+      </c>
+      <c r="H255" t="inlineStr">
+        <is>
+          <t>2026-06-17 16:12:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="n">
+        <v>8814</v>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>CR 72 H 37 D 35 SUR BRR CARVAJAL, Bogotá, 110861</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>in_transit</t>
+        </is>
+      </c>
+      <c r="E256" t="inlineStr">
+        <is>
+          <t>DET6403024974</t>
+        </is>
+      </c>
+      <c r="F256" t="inlineStr">
+        <is>
+          <t>https://trk.la/aXg1HNH</t>
+        </is>
+      </c>
+      <c r="G256" t="inlineStr">
+        <is>
+          <t>✅ Orden creada</t>
+        </is>
+      </c>
+      <c r="H256" t="inlineStr">
+        <is>
+          <t>2026-06-17 16:12:05</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="n">
+        <v>8813</v>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>CR 72 G  40  43 SUR, Bogotá, 00000</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>in_transit</t>
+        </is>
+      </c>
+      <c r="E257" t="inlineStr">
+        <is>
+          <t>DET6403024989</t>
+        </is>
+      </c>
+      <c r="F257" t="inlineStr">
+        <is>
+          <t>https://trk.la/aXg1Hm1</t>
+        </is>
+      </c>
+      <c r="G257" t="inlineStr">
+        <is>
+          <t>✅ Orden creada</t>
+        </is>
+      </c>
+      <c r="H257" t="inlineStr">
+        <is>
+          <t>2026-06-17 16:12:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="n">
+        <v>753</v>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>CR 24 23 78 P 2, Bogotá, 111411</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>in_transit</t>
+        </is>
+      </c>
+      <c r="E258" t="inlineStr">
+        <is>
+          <t>DET6403025004</t>
+        </is>
+      </c>
+      <c r="F258" t="inlineStr">
+        <is>
+          <t>https://trk.la/aXg1HQW</t>
+        </is>
+      </c>
+      <c r="G258" t="inlineStr">
+        <is>
+          <t>✅ Orden creada</t>
+        </is>
+      </c>
+      <c r="H258" t="inlineStr">
+        <is>
+          <t>2026-06-17 16:12:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="n">
+        <v>1640</v>
+      </c>
+      <c r="B259" t="inlineStr"/>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>Error</t>
+        </is>
+      </c>
+      <c r="E259" t="inlineStr"/>
+      <c r="F259" t="inlineStr"/>
+      <c r="G259" t="inlineStr">
+        <is>
+          <t>❌ Error en envío</t>
+        </is>
+      </c>
+      <c r="H259" t="inlineStr">
+        <is>
+          <t>2026-06-17 16:12:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="n">
+        <v>1639</v>
+      </c>
+      <c r="B260" t="inlineStr"/>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>Error</t>
+        </is>
+      </c>
+      <c r="E260" t="inlineStr"/>
+      <c r="F260" t="inlineStr"/>
+      <c r="G260" t="inlineStr">
+        <is>
+          <t>❌ Error en envío</t>
+        </is>
+      </c>
+      <c r="H260" t="inlineStr">
+        <is>
+          <t>2026-06-17 16:12:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>Test001</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Kra 77 N 71 - 43 </t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>in_transit</t>
+        </is>
+      </c>
+      <c r="E261" t="inlineStr">
+        <is>
+          <t>DET6403077113</t>
+        </is>
+      </c>
+      <c r="F261" t="inlineStr">
+        <is>
+          <t>https://trk.la/aXgp7Iz</t>
+        </is>
+      </c>
+      <c r="G261" t="inlineStr">
+        <is>
+          <t>✅ Orden creada</t>
+        </is>
+      </c>
+      <c r="H261" t="inlineStr">
+        <is>
+          <t>2026-06-17 23:39:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>Test001</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>krasd sdf df fd</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>in_transit</t>
+        </is>
+      </c>
+      <c r="E262" t="inlineStr">
+        <is>
+          <t>DET6403078362</t>
+        </is>
+      </c>
+      <c r="F262" t="inlineStr">
+        <is>
+          <t>https://trk.la/aXgS8Mi</t>
+        </is>
+      </c>
+      <c r="G262" t="inlineStr">
+        <is>
+          <t>✅ Orden creada</t>
+        </is>
+      </c>
+      <c r="H262" t="inlineStr">
+        <is>
+          <t>2026-06-17 23:52:57</t>
         </is>
       </c>
     </row>
